--- a/artfynd/A 19968-2026 artfynd.xlsx
+++ b/artfynd/A 19968-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123324432</v>
+        <v>123324433</v>
       </c>
       <c r="B2" t="n">
-        <v>58351</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +710,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598542</v>
+        <v>598543</v>
       </c>
       <c r="R2" t="n">
-        <v>6920620</v>
+        <v>6920652</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1182</t>
+          <t>2024_1181</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:33</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:33</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>juvenil</t>
+          <t>på sparad asp på hygge</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,15 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324433</v>
+        <v>123324432</v>
       </c>
       <c r="B3" t="n">
-        <v>91001</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,21 +816,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -850,7 +840,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598543</v>
+        <v>598542</v>
       </c>
       <c r="R3" t="n">
-        <v>6920652</v>
+        <v>6920620</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +879,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1181</t>
+          <t>2024_1182</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +899,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:33</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på sparad asp på hygge</t>
+          <t>juvenil</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -945,15 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123324411</v>
+        <v>123324408</v>
       </c>
       <c r="B4" t="n">
-        <v>97997</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -961,26 +946,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223591</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -994,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598608</v>
+        <v>598524</v>
       </c>
       <c r="R4" t="n">
-        <v>6920095</v>
+        <v>6920319</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1009,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1204</t>
+          <t>2024_1207</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1029,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>i gammal skogsväg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1080,15 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123324409</v>
+        <v>123324410</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,26 +1076,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1129,10 +1109,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598561</v>
+        <v>598600</v>
       </c>
       <c r="R5" t="n">
-        <v>6920190</v>
+        <v>6920130</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1139,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1206</t>
+          <t>2024_1205</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1169,7 +1149,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,12 +1159,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>i sänka</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1215,15 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123324408</v>
+        <v>123324409</v>
       </c>
       <c r="B6" t="n">
-        <v>97996</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,26 +1206,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1264,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598524</v>
+        <v>598561</v>
       </c>
       <c r="R6" t="n">
-        <v>6920319</v>
+        <v>6920190</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1294,7 +1269,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1207</t>
+          <t>2024_1206</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1304,7 +1279,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1314,12 +1289,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>i gammal skogsväg</t>
+          <t>i sänka</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1350,15 +1325,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123324410</v>
+        <v>123324411</v>
       </c>
       <c r="B7" t="n">
-        <v>97996</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99036</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,26 +1336,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>223591</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1399,10 +1369,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598600</v>
+        <v>598608</v>
       </c>
       <c r="R7" t="n">
-        <v>6920130</v>
+        <v>6920095</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1429,7 +1399,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1205</t>
+          <t>2024_1204</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1439,7 +1409,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1449,7 +1419,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 19968-2026 artfynd.xlsx
+++ b/artfynd/A 19968-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123324433</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -932,6 +942,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123324432</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1062,6 +1077,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123324408</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1192,6 +1212,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123324410</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1322,6 +1347,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123324409</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1452,8 +1482,21 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123324411</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>